--- a/info.xlsx
+++ b/info.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3795" yWindow="3510" windowWidth="24810" windowHeight="11385" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -26,15 +25,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -46,23 +53,33 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Κανονικό" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -425,8 +442,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16.85546875" customWidth="1" min="4" max="4"/>
+    <col width="25.7109375" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -481,28 +502,22 @@
           <t>οδοντιατροι</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2105736150</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>6942632569</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>2105736150</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6942632569</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LAGHIOS ADVANCED DENTISTRY</t>
+          <t>IMS DENTAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Παπαδιαμαντόπουλου Ιωάννη 4, Ιλίσια, 115 28 Αθήνα Αττικής </t>
+          <t xml:space="preserve">Πλάτωνος 8, Κέντρο, 152 34 Χαλάνδρι Αττικής </t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -510,28 +525,19 @@
           <t>οδοντιατροι</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2107213597</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>6944965696</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>2106828072</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>IMS DENTAL</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ABSOLUTE DENTAL CENTER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Πλάτωνος 8, Κέντρο, 152 34 Χαλάνδρι Αττικής </t>
+          <t xml:space="preserve">Σόλωνος 7, Κολωνάκι, 106 71 Αθήνα Αττικής </t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -539,24 +545,22 @@
           <t>οδοντιατροι</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2106828072</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>2103644903</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6978844744</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ABSOLUTE DENTAL CENTER</t>
+          <t>ΕΞΑΡΧΟΥ - ΤΡΙΑΝΤΑΦΥΛΛΟΥ ΝΑΤΑΣΣΑ DENTOLOGY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Σόλωνος 7, Κολωνάκι, 106 71 Αθήνα Αττικής </t>
+          <t xml:space="preserve">Ελευθερίου Βενιζέλου 72, Ευαγγελίστρια, 146 71 Νέα Ερυθραία Αττικής </t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -564,28 +568,22 @@
           <t>οδοντιατροι</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2103644903</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>6978844744</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>2106200150</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6987525656</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ΕΞΑΡΧΟΥ - ΤΡΙΑΝΤΑΦΥΛΛΟΥ ΝΑΤΑΣΣΑ DENTOLOGY</t>
+          <t>ΜΑΛΛΙΟΥ Ι. ΦΑΝΗ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ελευθερίου Βενιζέλου 72, Ευαγγελίστρια, 146 71 Νέα Ερυθραία Αττικής </t>
+          <t xml:space="preserve">Λεωφόρος Γαλατσίου 104, 111 46 Γαλάτσι Αττικής </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -593,28 +591,22 @@
           <t>οδοντιατροι</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2106200150</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>6987525656</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>2102932232</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6977244048</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ΜΑΛΛΙΟΥ Ι. ΦΑΝΗ</t>
+          <t>MEDICAL DENT - ΚΙΜΙΩΝΗΣ ΑΛΕΞΑΝΔΡΟΣ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Λεωφόρος Γαλατσίου 104, 111 46 Γαλάτσι Αττικής </t>
+          <t xml:space="preserve">Καισαρείας 6, Ιλίσια, 115 27 Αθήνα Αττικής </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -622,28 +614,19 @@
           <t>οδοντιατροι</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2102932232</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>6977244048</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>2107487200</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MEDICAL DENT - ΚΙΜΙΩΝΗΣ ΑΛΕΞΑΝΔΡΟΣ</t>
+          <t>ΚΥΡΙΑΖΟΣ ΑΛΚΗΣ - YOUR DENTAL CARE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Καισαρείας 6, Ιλίσια, 115 27 Αθήνα Αττικής </t>
+          <t xml:space="preserve">Λεωφόρος Κηφισίας 135 &amp; Λάμψα 1, Αμπελόκηποι, 115 24 Αθήνα Αττικής </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -651,24 +634,22 @@
           <t>οδοντιατροι</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2107487200</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>2106916337</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6937131148</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ΚΥΡΙΑΖΟΣ ΑΛΚΗΣ - YOUR DENTAL CARE</t>
+          <t>THE DENTAL CLINIC - ΚΑΛΤΣΑΣ ΑΛΕΞΑΝΔΡΟΣ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Λεωφόρος Κηφισίας 135 &amp; Λάμψα 1, Αμπελόκηποι, 115 24 Αθήνα Αττικής </t>
+          <t xml:space="preserve">Λεωφόρος Κηφισίας 238, Τρίγωνο Αγίας Βαρβάρας, 152 31 Χαλάνδρι Αττικής </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -676,28 +657,22 @@
           <t>οδοντιατροι</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2106916337</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>6937131148</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>2106745832</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6944293840</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>THE DENTAL CLINIC - ΚΑΛΤΣΑΣ ΑΛΕΞΑΝΔΡΟΣ</t>
+          <t>ΠΟΛΥΟΔΟΝΤΙΑΤΡΕΙΟ DENTAL PLUS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Λεωφόρος Κηφισίας 238, Τρίγωνο Αγίας Βαρβάρας, 152 31 Χαλάνδρι Αττικής </t>
+          <t xml:space="preserve">Λεωφόρος Μαραθώνος 46, 153 51 Παλλήνη Αττικής </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -705,28 +680,22 @@
           <t>οδοντιατροι</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2106745832</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>6944293840</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>2106669960</v>
+      </c>
+      <c r="E10" t="n">
+        <v>6937605464</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ΠΟΛΥΟΔΟΝΤΙΑΤΡΕΙΟ DENTAL PLUS</t>
+          <t>COSMETIC DENTAL CLINIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Λεωφόρος Μαραθώνος 46, 153 51 Παλλήνη Αττικής </t>
+          <t xml:space="preserve">Λεωφόρος Βασιλίσσης Σοφίας 54, Ιλίσια, 115 28 Αθήνα Αττικής </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -734,28 +703,19 @@
           <t>οδοντιατροι</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2106669960</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>6937605464</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>2107296039</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COSMETIC DENTAL CLINIC</t>
+          <t>ΒΑΤΣΕΛΑ Π. ΕΛΕΝΗ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Λεωφόρος Βασιλίσσης Σοφίας 54, Ιλίσια, 115 28 Αθήνα Αττικής </t>
+          <t xml:space="preserve">Μελίνας Μερκούρη 20, Άγιοι Ταξιάρχες, 141 22 Ηράκλειο Αττικής </t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -763,24 +723,22 @@
           <t>οδοντιατροι</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2107296039</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>2108216301</v>
+      </c>
+      <c r="E12" t="n">
+        <v>6973787992</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ΒΑΤΣΕΛΑ Π. ΕΛΕΝΗ</t>
+          <t>THE DENTAL HOME</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Μελίνας Μερκούρη 20, Άγιοι Ταξιάρχες, 141 22 Ηράκλειο Αττικής </t>
+          <t xml:space="preserve">Λεωφόρος Περικλέους 27, 155 61 Χολαργός Αττικής </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -788,28 +746,22 @@
           <t>οδοντιατροι</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2108216301</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>6973787992</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>2106523754</v>
+      </c>
+      <c r="E13" t="n">
+        <v>6972604744</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>THE DENTAL HOME</t>
+          <t>ΛΑΤΙΝΟΣ ΦΩΤΗΣ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Λεωφόρος Περικλέους 27, 155 61 Χολαργός Αττικής </t>
+          <t xml:space="preserve">Βυζαντινών Αυτοκρατόρων 11, Περισσός, 142 32 Νέα Ιωνία Αττικής </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -817,28 +769,22 @@
           <t>οδοντιατροι</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2106523754</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>6972604744</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>2102581771</v>
+      </c>
+      <c r="E14" t="n">
+        <v>6974307559</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ΛΑΤΙΝΟΣ ΦΩΤΗΣ</t>
+          <t>ΒΟΓΙΑΤΖΟΓΛΟΥ ΔΗΜΗΤΡΑ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Βυζαντινών Αυτοκρατόρων 11, Περισσός, 142 32 Νέα Ιωνία Αττικής </t>
+          <t xml:space="preserve">Αριστοτέλους 187, 136 78 Αχαρνές Αττικής </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -846,28 +792,22 @@
           <t>οδοντιατροι</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2102581771</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>6974307559</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>2102464408</v>
+      </c>
+      <c r="E15" t="n">
+        <v>6985689935</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ΒΟΓΙΑΤΖΟΓΛΟΥ ΔΗΜΗΤΡΑ</t>
+          <t>LAGHIOS ADVANCED DENTISTRY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Αριστοτέλους 187, 136 78 Αχαρνές Αττικής </t>
+          <t xml:space="preserve">Παπαδιαμαντόπουλου Ιωάννη 4, Ιλίσια, 115 28 Αθήνα Αττικής </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -875,18 +815,12 @@
           <t>οδοντιατροι</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2102464408</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>6985689935</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>2107213597</v>
+      </c>
+      <c r="E16" t="n">
+        <v>6944965696</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -904,28 +838,22 @@
           <t>οδοντιατροι</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2106439390</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>6943011864</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>2106439390</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6943011864</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ΜΑΡΓΑΡΙΤΗ ΜΑΡΙΑ - DENTAL PROLIPSIS</t>
+          <t>ΚΑΚΛΑΜΑΝΗΣ ΑΓΓΕΛΟΣ - ΠΟΛΥΟΔΟΝΤΙΑΤΡΕΙΟ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Μπουμπουλίνας 2Α, Αγία Ελεούσα, 176 75 Καλλιθέα Αττικής </t>
+          <t xml:space="preserve">Λεωφόρος Θηβών 210, 121 34 Περιστέρι Αττικής </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -933,28 +861,19 @@
           <t>οδοντιατροι</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2109583535</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>6976215741</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>2105730784</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ΚΑΚΛΑΜΑΝΗΣ ΑΓΓΕΛΟΣ - ΠΟΛΥΟΔΟΝΤΙΑΤΡΕΙΟ</t>
+          <t>ΜΑΡΓΑΡΙΤΗ ΜΑΡΙΑ - DENTAL PROLIPSIS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Λεωφόρος Θηβών 210, 121 34 Περιστέρι Αττικής </t>
+          <t xml:space="preserve">Μπουμπουλίνας 2Α, Αγία Ελεούσα, 176 75 Καλλιθέα Αττικής </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -962,24 +881,22 @@
           <t>οδοντιατροι</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2105730784</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>2109583535</v>
+      </c>
+      <c r="E19" t="n">
+        <v>6976215741</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ΑΝΤΩΝΟΓΙΑΝΝΑΚΗ ΕΥΑΓΓΕΛΙΑ - A-PERIO</t>
+          <t>ΚΑΡΔΑΤΟΥ ΡΟΔΟΠΗ - ΜΑΡΙΑ DMD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Αναστάσεως 85, Άνω Χολαργός, 155 61 Χολαργός Αττικής </t>
+          <t xml:space="preserve">Λεωφόρος Κύπρου 117, 164 51 Αργυρούπολη Αττικής </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -987,24 +904,22 @@
           <t>οδοντιατροι</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2106528761</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>2107298955</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6937433366</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ΚΑΡΔΑΤΟΥ ΡΟΔΟΠΗ - ΜΑΡΙΑ DMD</t>
+          <t>ΑΝΤΩΝΟΓΙΑΝΝΑΚΗ ΕΥΑΓΓΕΛΙΑ - A-PERIO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Λεωφόρος Κύπρου 117, 164 51 Αργυρούπολη Αττικής </t>
+          <t xml:space="preserve">Αναστάσεως 85, Άνω Χολαργός, 155 61 Χολαργός Αττικής </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1012,68 +927,12 @@
           <t>οδοντιατροι</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2107298955</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>6937433366</t>
-        </is>
-      </c>
+      <c r="D21" t="n">
+        <v>2106528761</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>ΑΛΕΒΙΖΟΣ ΑΚΗΣ</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Αγίας Φωτεινής 57, Άγιοι Ανάργυροι, 142 31 Νέα Ιωνία Αττικής </t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>οδοντιατροι</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>6972131704</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>ΟΙΚΟΝΟΜΟΥ ΗΛΙΑΣ DDS, MSc - PERIO &amp; ORTHO</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Φειδιππίδου 8, Αμπελόκηποι, 115 26 Αθήνα Αττικής </t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>οδοντιατροι</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2107770620</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/info.xlsx
+++ b/info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\webapp\xo_webscraper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7716770-CC05-44A5-A17A-DFD872BCBF6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD894A0-FAE5-4B20-AC3C-3929472C251C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3795" yWindow="3510" windowWidth="24810" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="87">
   <si>
     <t>Name</t>
   </si>
@@ -220,6 +220,60 @@
     <t>6976215741</t>
   </si>
   <si>
+    <t>ΑΝΤΩΝΟΓΙΑΝΝΑΚΗ ΕΥΑΓΓΕΛΙΑ - A-PERIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Αναστάσεως 85, Άνω Χολαργός, 155 61 Χολαργός Αττικής </t>
+  </si>
+  <si>
+    <t>2106528761</t>
+  </si>
+  <si>
+    <t>ΚΑΡΔΑΤΟΥ ΡΟΔΟΠΗ - ΜΑΡΙΑ DMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Λεωφόρος Κύπρου 117, 164 51 Αργυρούπολη Αττικής </t>
+  </si>
+  <si>
+    <t>2107298955</t>
+  </si>
+  <si>
+    <t>ΑΛΕΒΙΖΟΣ ΑΚΗΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Αγίας Φωτεινής 57, Άγιοι Ανάργυροι, 142 31 Νέα Ιωνία Αττικής </t>
+  </si>
+  <si>
+    <t>6972131704</t>
+  </si>
+  <si>
+    <t>ΟΙΚΟΝΟΜΟΥ ΗΛΙΑΣ DDS, MSc - PERIO &amp; ORTHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Φειδιππίδου 8, Αμπελόκηποι, 115 26 Αθήνα Αττικής </t>
+  </si>
+  <si>
+    <t>2107770620</t>
+  </si>
+  <si>
+    <t>ABSOLUTE DENTAL CENTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Σόλωνος 7, Κολωνάκι, 106 71 Αθήνα Αττικής </t>
+  </si>
+  <si>
+    <t>6978844744</t>
+  </si>
+  <si>
+    <t>MEDICAL DENT - ΚΙΜΙΩΝΗΣ ΑΛΕΞΑΝΔΡΟΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Καισαρείας 6, Ιλίσια, 115 27 Αθήνα Αττικής </t>
+  </si>
+  <si>
+    <t>2107487200</t>
+  </si>
+  <si>
     <t>ΚΑΚΛΑΜΑΝΗΣ ΑΓΓΕΛΟΣ - ΠΟΛΥΟΔΟΝΤΙΑΤΡΕΙΟ</t>
   </si>
   <si>
@@ -227,63 +281,6 @@
   </si>
   <si>
     <t>2105730784</t>
-  </si>
-  <si>
-    <t>ΑΝΤΩΝΟΓΙΑΝΝΑΚΗ ΕΥΑΓΓΕΛΙΑ - A-PERIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Αναστάσεως 85, Άνω Χολαργός, 155 61 Χολαργός Αττικής </t>
-  </si>
-  <si>
-    <t>2106528761</t>
-  </si>
-  <si>
-    <t>ΚΑΡΔΑΤΟΥ ΡΟΔΟΠΗ - ΜΑΡΙΑ DMD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Λεωφόρος Κύπρου 117, 164 51 Αργυρούπολη Αττικής </t>
-  </si>
-  <si>
-    <t>2107298955</t>
-  </si>
-  <si>
-    <t>6937433366</t>
-  </si>
-  <si>
-    <t>ΑΛΕΒΙΖΟΣ ΑΚΗΣ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Αγίας Φωτεινής 57, Άγιοι Ανάργυροι, 142 31 Νέα Ιωνία Αττικής </t>
-  </si>
-  <si>
-    <t>6972131704</t>
-  </si>
-  <si>
-    <t>ΟΙΚΟΝΟΜΟΥ ΗΛΙΑΣ DDS, MSc - PERIO &amp; ORTHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Φειδιππίδου 8, Αμπελόκηποι, 115 26 Αθήνα Αττικής </t>
-  </si>
-  <si>
-    <t>2107770620</t>
-  </si>
-  <si>
-    <t>ABSOLUTE DENTAL CENTER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Σόλωνος 7, Κολωνάκι, 106 71 Αθήνα Αττικής </t>
-  </si>
-  <si>
-    <t>2103644903</t>
-  </si>
-  <si>
-    <t>6978844744</t>
-  </si>
-  <si>
-    <t>MEDICAL DENT - ΚΙΜΙΩΝΗΣ ΑΛΕΞΑΝΔΡΟΣ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Καισαρείας 6, Ιλίσια, 115 27 Αθήνα Αττικής </t>
   </si>
 </sst>
 </file>
@@ -658,6 +655,7 @@
   <cols>
     <col min="3" max="3" width="11.5703125" customWidth="1"/>
     <col min="4" max="4" width="14.85546875" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -959,6 +957,9 @@
       <c r="D18" t="s">
         <v>71</v>
       </c>
+      <c r="E18">
+        <v>6937433366</v>
+      </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -973,67 +974,64 @@
       <c r="D19" t="s">
         <v>74</v>
       </c>
-      <c r="E19" t="s">
-        <v>75</v>
-      </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" t="s">
         <v>76</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" t="s">
         <v>77</v>
-      </c>
-      <c r="C20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" t="s">
         <v>79</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21">
+        <v>2103644903</v>
+      </c>
+      <c r="E21" t="s">
         <v>80</v>
-      </c>
-      <c r="C21" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" t="s">
         <v>82</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" t="s">
         <v>83</v>
-      </c>
-      <c r="C22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" t="s">
-        <v>84</v>
-      </c>
-      <c r="E22" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" t="s">
         <v>86</v>
-      </c>
-      <c r="B23" t="s">
-        <v>87</v>
-      </c>
-      <c r="C23" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23">
-        <v>2107487200</v>
       </c>
     </row>
   </sheetData>

--- a/info.xlsx
+++ b/info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\webapp\xo_webscraper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD894A0-FAE5-4B20-AC3C-3929472C251C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D4914B0-15BB-4BF0-BBEC-E62CEC9FE036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3795" yWindow="3510" windowWidth="24810" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="380">
   <si>
     <t>Name</t>
   </si>
@@ -281,6 +281,885 @@
   </si>
   <si>
     <t>2105730784</t>
+  </si>
+  <si>
+    <t>LASER DENTAL CLINIC - ΤΖΑΝΝΟΥ ΕΥΣΤΡΑΤΙΟΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Πατριάρχου Γρηγορίου Ε΄ 49, 142 31 Νέα Ιωνία Αττικής </t>
+  </si>
+  <si>
+    <t>2102797204</t>
+  </si>
+  <si>
+    <t>ΚΟΜΗ ΕΙΡΗΝΗ - ΛΙΝΤΙΤΑ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Αναστάσιου Μανάκη 28, Ριμινιτών - Ευαγγελίστρια, 131 22 Ίλιον (ή Νέα Λιόσια) Αττικής </t>
+  </si>
+  <si>
+    <t>2130240669</t>
+  </si>
+  <si>
+    <t>6942849986</t>
+  </si>
+  <si>
+    <t>SMILE HARMONY - ΤΣΟΠΑΚΗ ΣΤΕΛΛΑ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Δελφών 18 &amp; Βεάκη Αιμίλιου, 3ος Όροφος, 121 34 Περιστέρι Αττικής </t>
+  </si>
+  <si>
+    <t>2105722547</t>
+  </si>
+  <si>
+    <t>6980741553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ξάνθου Εμμανουήλ 2 &amp; Αναγνωστόπουλου Παναγιώτη, Κολωνάκι, 106 73 Αθήνα Αττικής </t>
+  </si>
+  <si>
+    <t>2107224555</t>
+  </si>
+  <si>
+    <t>SOUTH ATHENS DENTAL CLINIC - ΔΕΣΠΟΤΑΚΗΣ Ι. ΕΜΜΑΝΟΥΗΛ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Λεωφ. Ελευθερίου Βενιζέλου 344 &amp; Λεωφ. Ποσειδώνος, 176 75 Καλλιθέα Αττικής </t>
+  </si>
+  <si>
+    <t>2109426431</t>
+  </si>
+  <si>
+    <t>ΤΡΙΑΝΤΑΦΥΛΛΟΥ Κ. ΤΡΙΑΝΤΑΦΥΛΛΟΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Φεραίου Ρήγα 72, Χαροκόπου, 176 72 Καλλιθέα Αττικής </t>
+  </si>
+  <si>
+    <t>2109576495</t>
+  </si>
+  <si>
+    <t>6932357116</t>
+  </si>
+  <si>
+    <t>ΠΑΠΑΔΟΠΟΥΛΟΣ ΜΑΡΙΝΟΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ιωάννη Παπαδιαμαντόπουλου 14, Ιλίσια, 115 28 Αθήνα Αττικής </t>
+  </si>
+  <si>
+    <t>2107293473</t>
+  </si>
+  <si>
+    <t>6944886813</t>
+  </si>
+  <si>
+    <t>ΑΛΗΣΑΦΗΣ ΜΙΧΑΗΛ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Λεωφόρος Βενιζέλου Ελευθέριου 77, Παναγία, 163 43 Ηλιούπολη Αττικής </t>
+  </si>
+  <si>
+    <t>2109923106</t>
+  </si>
+  <si>
+    <t>6972873700</t>
+  </si>
+  <si>
+    <t>ΔΑΜΟΥΛΗΣ ΠΕΤΡΟΣ DDS, DMD, DMSc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Λεωφόρος Κηφισίας 176 &amp; Αιμίλιου Βεάκη 1, Ελληνορώσων, 115 25 Αθήνα Αττικής </t>
+  </si>
+  <si>
+    <t>2106771793</t>
+  </si>
+  <si>
+    <t>S.D.A - LOLIS CHRISTOS Dr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ψυχάρη 1, Αγία Σοφία, 154 51 Νέο Ψυχικό Αττικής </t>
+  </si>
+  <si>
+    <t>2106741600</t>
+  </si>
+  <si>
+    <t>DENTAL OASIS ΤΡΑΠΑΛΗΣ Ι .- ΤΟΥΡΝΑΣ Ν.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ορφανίδου 9, Άνω Πατήσια, 111 42 Αθήνα Αττικής </t>
+  </si>
+  <si>
+    <t>2102283882</t>
+  </si>
+  <si>
+    <t>6937008750</t>
+  </si>
+  <si>
+    <t>DENTAL SLEEP MEDICINE - ΤΣΟΥΤΗΣ ΚΩΝΣΤΑΝΤΙΝΟΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Σεμιτέλου Δημήτριου 6, Ιλίσια, 115 28 Αθήνα Αττικής </t>
+  </si>
+  <si>
+    <t>2107702192</t>
+  </si>
+  <si>
+    <t>6974683841</t>
+  </si>
+  <si>
+    <t>ΒΟΛΤΙΔΗ ΕΛΕΝΗ DDS, MSc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Θερμοπυλών 4-6, Κέντρο, 151 24 Μαρούσι Αττικής </t>
+  </si>
+  <si>
+    <t>2106126379</t>
+  </si>
+  <si>
+    <t>6979446176</t>
+  </si>
+  <si>
+    <t>ΔΑΒΑΛΟΥ - ΜΗΤΡΟΥ ΣΤΑΥΡΟΥΛΑ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Μενάνδρου 4 &amp; Ηρώδου Αττικού, 145 61 Κηφισιά Αττικής </t>
+  </si>
+  <si>
+    <t>2106231310</t>
+  </si>
+  <si>
+    <t>ΠΟΥΛΙΟΣ ΑΝΑΡΓΥΡΟΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Λεωφόρος Βενιζέλου Ελευθέριου (Λεωφόρος Θησέως) 260, 176 75 Καλλιθέα Αττικής </t>
+  </si>
+  <si>
+    <t>2109407880</t>
+  </si>
+  <si>
+    <t>6972015082</t>
+  </si>
+  <si>
+    <t>DENTAL FAMILY HEALTH - ΚΑΚΛΑΜΑΝΗΣ ΑΓΓΕΛΟΣ &amp; ΣΥΝΕΡΓΑΤΕΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Λεωφόρος Ειρήνης 28 &amp; Βρυούλων, Άγιος Παντελεήμονας, 151 21 Πεύκη Αττικής </t>
+  </si>
+  <si>
+    <t>2106122244</t>
+  </si>
+  <si>
+    <t>6943762629</t>
+  </si>
+  <si>
+    <t>ΔΕΛΕΝΔΑΣ ΝΙΚΟΛΑΟΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ριανκούρ 75 - 81, Αμπελόκηποι, 115 24 Αθήνα Αττικής </t>
+  </si>
+  <si>
+    <t>2106984382</t>
+  </si>
+  <si>
+    <t>ΧΑΜΠΑΖ Γ. ΜΑΡΟΥΑΝ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Πεντέλης 40, 151 26 Μαρούσι Αττικής </t>
+  </si>
+  <si>
+    <t>2108052382</t>
+  </si>
+  <si>
+    <t>ΚΑΚΑΪΔΗΣ ΑΛΕΞΑΝΔΡΟΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Λεωφόρος Κύπρου 47 &amp; Τσαλδάρη, Νέο Παγκράτι, 162 32 Βύρωνας Αττικής </t>
+  </si>
+  <si>
+    <t>2107643276</t>
+  </si>
+  <si>
+    <t>6977829706</t>
+  </si>
+  <si>
+    <t>IN DENTISTRY WE TRUST - ΛΟΥΚΑ ΜΑΡΙΑ - ΑΝΝΕΖΑ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Λεωφόρος Ειρήνης 6, Άγιος Παντελεήμονας, 151 21 Πεύκη Αττικής </t>
+  </si>
+  <si>
+    <t>2114002560</t>
+  </si>
+  <si>
+    <t>6946258562</t>
+  </si>
+  <si>
+    <t>ΠΑΡΑΣΙΔΟΥ Α. ΔΕΣΠΟΙΝΑ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Αγίου Ιωάννη 65 &amp; Ελευθερίας 2, Κέντρο, Είσοδος από Ελευθερίας 2, 153 42 Αγία Παρασκευή Αττικής </t>
+  </si>
+  <si>
+    <t>2106014672</t>
+  </si>
+  <si>
+    <t>6974090272</t>
+  </si>
+  <si>
+    <t>ΔΟΥΡΟΥ ΒΑΣΙΛΙΚΗ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Αγησιλάου 20, 176 74 Καλλιθέα Αττικής </t>
+  </si>
+  <si>
+    <t>2109404665</t>
+  </si>
+  <si>
+    <t>6974717956</t>
+  </si>
+  <si>
+    <t>ΒΡΕΤΤΟΣ Ι. ΣΩΤΗΡΙΟΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Λεωφόρος Μεσογείων 421Α, 153 43 Αγία Παρασκευή Αττικής </t>
+  </si>
+  <si>
+    <t>2130408042</t>
+  </si>
+  <si>
+    <t>6973248891</t>
+  </si>
+  <si>
+    <t>MATSOUKA DENTAL CLINIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Αμαζόνων 46, Σούρμενα, 167 77 Ελληνικό Αττικής </t>
+  </si>
+  <si>
+    <t>2109602070</t>
+  </si>
+  <si>
+    <t>6975208484</t>
+  </si>
+  <si>
+    <t>ΠΑΓΩΝΑΣ ΣΠΥΡΙΔΩΝ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Λεωφόρος Δεκελείας 33, 136 74 Αχαρνές Αττικής </t>
+  </si>
+  <si>
+    <t>2102447333</t>
+  </si>
+  <si>
+    <t>ΣΠΥΡΟΠΟΥΛΟΥ ΝΟΤΑ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Πολυτεχνείου 32, 141 22 Ηράκλειο Αττικής </t>
+  </si>
+  <si>
+    <t>2102827360</t>
+  </si>
+  <si>
+    <t>6937727381</t>
+  </si>
+  <si>
+    <t>ΚΑΤΣΑΡΩΝΗΣ Γ ΠΑΥΛΟΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ευριπίδου 18 &amp; Θησέως, 141 22 Ηράκλειο Αττικής </t>
+  </si>
+  <si>
+    <t>2102847691</t>
+  </si>
+  <si>
+    <t>6977001534</t>
+  </si>
+  <si>
+    <t>ΛΙΩΛΙΑΚΗΣ ΑΝΔΡΕΑΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Σμύρνης 55, 122 42 Αιγάλεω Αττικής </t>
+  </si>
+  <si>
+    <t>2105910178</t>
+  </si>
+  <si>
+    <t>6948541651</t>
+  </si>
+  <si>
+    <t>ΜΑΤΣΙΝΟΣ Γ. ΣΤΑΜΑΤΗΣ DDS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Λεωφόρος Παναγιώτη Πρωτόπαπα 43, Παναγία, 163 43 Ηλιούπολη Αττικής </t>
+  </si>
+  <si>
+    <t>2109615022</t>
+  </si>
+  <si>
+    <t>6932525483</t>
+  </si>
+  <si>
+    <t>ΔΟΡΚΟΦΥΚΗ ΕΛΙΑ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ζωοδόχου Πηγής 43, Εξάρχεια, 106 81 Αθήνα Αττικής </t>
+  </si>
+  <si>
+    <t>2103304510</t>
+  </si>
+  <si>
+    <t>ΤΡΑΚΑΣ ΘΕΟΔΩΡΟΣ - ORAL HEALTH CARE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Μιχαλακοπούλου 45, Ιλίσια, 115 28 Αθήνα Αττικής </t>
+  </si>
+  <si>
+    <t>2107245571</t>
+  </si>
+  <si>
+    <t>6944464882</t>
+  </si>
+  <si>
+    <t>ΠΡΟΕΣΤΑΚΗ ΣΤΥΛΙΑΝΗ - ΚΩΝΣΤΑΝΤΙΝΑ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Λεωφόρος Πάρνηθος 82Β, 3ος όροφος, 136 74 Αχαρνές Αττικής </t>
+  </si>
+  <si>
+    <t>2102449001</t>
+  </si>
+  <si>
+    <t>6986822176</t>
+  </si>
+  <si>
+    <t>ΤΣΑΓΚΑΡΗ ΝΕΦΕΛΗ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Πριάμου 6, Παναγίτσα, 173 43 Άγιος Δημήτριος Αττικής </t>
+  </si>
+  <si>
+    <t>2112152050</t>
+  </si>
+  <si>
+    <t>6947824474</t>
+  </si>
+  <si>
+    <t>ATHENS DENTAL PROJECT - ΜΠΟΥΛΝΤΗΣ ΓΙΩΡΓΟΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Υμηττού 1 &amp; Λεωφόρος Βουλιαγμένης 604, 167 77 Ελληνικό Αττικής </t>
+  </si>
+  <si>
+    <t>2111196707</t>
+  </si>
+  <si>
+    <t>6978507450</t>
+  </si>
+  <si>
+    <t>ΚΑΡΑΜΑΝΟΥ ΕΥΑΓΓΕΛΙΑ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Αργοστολίου 113 &amp; Λευκών Ορέων 53, 173 42 Άγιος Δημήτριος Αττικής </t>
+  </si>
+  <si>
+    <t>2109887817</t>
+  </si>
+  <si>
+    <t>6937316704</t>
+  </si>
+  <si>
+    <t>ΚΡΟΜΜΥΔΑΣ ΜΑΡΙΟΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Λεωφόρος Δήμαρχου Μεταξά Άγγελου 21, Ευρυάλη, 166 75 Γλυφάδα Αττικής </t>
+  </si>
+  <si>
+    <t>2108983243</t>
+  </si>
+  <si>
+    <t>6972328262</t>
+  </si>
+  <si>
+    <t>ΠΑΡΑΣΚΕΥΑΣ ΙΩΑΝΝΗΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Αχιλλέως 42, Παναγίτσα, 175 62 Παλαιό Φάληρο Αττικής </t>
+  </si>
+  <si>
+    <t>2109811443</t>
+  </si>
+  <si>
+    <t>6936606994</t>
+  </si>
+  <si>
+    <t>THE SMILE MAKERS - ΜΟΥΛΑΒΑΣΙΛΗ - ΜΠΑΡΔΗ ΠΑΝΑΓΙΩΤΑ Dr - ΜΠΑΡΔΗΣ ΔΗΜΗΤΡΙΟΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Επιδαύρου 67, Αγία Τριάδα, 122 43 Αιγάλεω Αττικής </t>
+  </si>
+  <si>
+    <t>2105904711</t>
+  </si>
+  <si>
+    <t>6977970700</t>
+  </si>
+  <si>
+    <t>ΠΑΠΑΠΑΝΑΓΙΩΤΟΥ ΔΗΜΗΤΡΙΟΣ DMD - MSc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Πλατεία Δημοκρατίας 2, 145 65 Άγιος Στέφανος Αττικής </t>
+  </si>
+  <si>
+    <t>2108141533</t>
+  </si>
+  <si>
+    <t>6974587863</t>
+  </si>
+  <si>
+    <t>ΦΑΣΚΙΩΤΗΣ ΚΩΝΣΤΑΝΤΙΝΟΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Κοραή Αδαμάντιου 8, Νέο Αιγάλεω, 122 41 Αιγάλεω Αττικής </t>
+  </si>
+  <si>
+    <t>2105621710</t>
+  </si>
+  <si>
+    <t>6944791593</t>
+  </si>
+  <si>
+    <t>ΚΩΝΣΤΑΝΤΟΠΟΥΛΟΥ ΓΕΩΡΓΙΑ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Παπαφλέσσα 57-59 &amp; Ευρυδίκης 1, Λαμπρινή, 111 46 Γαλάτσι Αττικής </t>
+  </si>
+  <si>
+    <t>2102931589</t>
+  </si>
+  <si>
+    <t>6974388095</t>
+  </si>
+  <si>
+    <t>ΦΡΑΝΤΖΕΣΚΑΚΗΣ ΑΝΑΣΤΑΣΙΟΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ροδοδάφνης 3, Πολύδροσο, 152 33 Χαλάνδρι Αττικής </t>
+  </si>
+  <si>
+    <t>2106895399</t>
+  </si>
+  <si>
+    <t>6973667944</t>
+  </si>
+  <si>
+    <t>ΜΕΓΑΣ Φ. ΒΑΣΙΛΕΙΟΣ - ΜΕΓΑΣ Β. ΛΑΜΠΡΟΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Φαιδριάδων 104-106, Άνω Κυψέλη, 1ος όροφος, 113 64 Αθήνα Αττικής </t>
+  </si>
+  <si>
+    <t>2108614432</t>
+  </si>
+  <si>
+    <t>6944545488</t>
+  </si>
+  <si>
+    <t>ΑΝΤΩΝΟΠΟΥΛΟΥ ΑΝΑΣΤΑΣΙΑ - DENTAL CARE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Γρηγορίου Λαμπράκη 21, Ευρυάλη, 166 75 Γλυφάδα Αττικής </t>
+  </si>
+  <si>
+    <t>2109629957</t>
+  </si>
+  <si>
+    <t>6944137042</t>
+  </si>
+  <si>
+    <t>MIRACLE SMILES BY DR SOULTANIS IN GLYFADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Βασιλίσσης Όλγας 35 &amp; Γούναρη Δημήτριου 137, 165 61 Γλυφάδα Αττικής </t>
+  </si>
+  <si>
+    <t>2109649605</t>
+  </si>
+  <si>
+    <t>6948532887</t>
+  </si>
+  <si>
+    <t>ΤΕΠΕΤΖΙΚΙΩΤΗΣ ΓΕΩΡΓΙΟΣ - ΜΠΑΣΔΕΚΗ ΕΙΡΗΝΗ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Καρτάλη 8, Ιλίσια, 115 28 Αθήνα Αττικής </t>
+  </si>
+  <si>
+    <t>2107715579</t>
+  </si>
+  <si>
+    <t>6977401200</t>
+  </si>
+  <si>
+    <t>DENTAL CLINIC BY KOLIOULI ELENI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Βελβενδού 12, Κυψέλη, 113 63 Αθήνα Αττικής </t>
+  </si>
+  <si>
+    <t>2108822688</t>
+  </si>
+  <si>
+    <t>6948051391</t>
+  </si>
+  <si>
+    <t>ATHENS ENDODONTIC CARE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Σουλίου 1 &amp; Λεωφόρος Βουλιαγμένης 326, 173 42 Άγιος Δημήτριος Αττικής </t>
+  </si>
+  <si>
+    <t>2130462319</t>
+  </si>
+  <si>
+    <t>ΞΕΝΙΔΟΥ - DENTAL CLINIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Εθνικής Αντιστάσεως 73, 132 31 Πετρούπολη Αττικής </t>
+  </si>
+  <si>
+    <t>2105010050</t>
+  </si>
+  <si>
+    <t>ΦΩΤΟΠΟΥΛΟΣ ΘΕΟΔΩΡΟΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Λεωφόρος Βασιλέως Γεωργίου Β΄ 42, Παγκράτι, 116 34 Αθήνα Αττικής </t>
+  </si>
+  <si>
+    <t>2107222310</t>
+  </si>
+  <si>
+    <t>6974380477</t>
+  </si>
+  <si>
+    <t>ΔΗΜΑΚΗΣ ΑΘΑΝΑΣΙΟΣ DDS, MSc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28ης Οκτωβρίου (Πατησίων) 141 &amp; Κεφαλληνίας, Άγιος Παντελεήμονας, 112 51 Αθήνα Αττικής </t>
+  </si>
+  <si>
+    <t>2108224762</t>
+  </si>
+  <si>
+    <t>6947305086</t>
+  </si>
+  <si>
+    <t>ΜΟΥΤΑΦΙΔΟΥ ΜΑΡΙΑ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Χελμού 56 &amp; Ύδρας, Βιομηχανική Περιοχή, 145 65 Άγιος Στέφανος (ή Νέο Μπογιάτι) Αττικής </t>
+  </si>
+  <si>
+    <t>2117350094</t>
+  </si>
+  <si>
+    <t>6977301520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ανδρίκου Λάμπρου 2, Κέντρο, 190 02 Παιανία Αττικής </t>
+  </si>
+  <si>
+    <t>2106640515</t>
+  </si>
+  <si>
+    <t>2106719775</t>
+  </si>
+  <si>
+    <t>6937053303</t>
+  </si>
+  <si>
+    <t>ΓΕΩΡΓΑΚΑΚΟΥ ΓΡΗΓΟΡΙΑ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Λυσίου 3, Άγιος Κωνσταντίνος, 163 46 Ηλιούπολη Αττικής </t>
+  </si>
+  <si>
+    <t>2109761128</t>
+  </si>
+  <si>
+    <t>6944909772</t>
+  </si>
+  <si>
+    <t>ΚΑΠΕΛΛΕΣ Ν. ΣΠΥΡΙΔΩΝ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Θεσσαλονίκης &amp; Πηνειού 1, Πλατεία Δημοκρατίας, 134 51 Καματερό Αττικής </t>
+  </si>
+  <si>
+    <t>2102380562</t>
+  </si>
+  <si>
+    <t>6972487907</t>
+  </si>
+  <si>
+    <t>ΖΑΦΕΙΡΟΠΟΥΛΟΣ ΑΓΓΕΛΟΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Κατεχάκη 1 &amp; Μεσογείων, Έναντι Μετρό Σταθμός Κατεχάκη, 115 25 Αθήνα Αττικής </t>
+  </si>
+  <si>
+    <t>2106995535</t>
+  </si>
+  <si>
+    <t>6972072076</t>
+  </si>
+  <si>
+    <t>ΔΡΟΥΚΑΣ Χ. ΒΥΡΩΝ ΔΡ.</t>
+  </si>
+  <si>
+    <t>2107244002</t>
+  </si>
+  <si>
+    <t>6944775686</t>
+  </si>
+  <si>
+    <t>LUXESTH ΣΥΓΧΡΟΝΗ ΟΔΟΝΤΙΑΤΡΙΚΗ - GIORGADZE ΑΝΝΑ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Βενιζέλου Ελευθέριου 22 &amp; Πρωτοπαπαδάκη Πέτρου, Γωνία, 1ος ¨Οροφος, 111 47 Γαλάτσι Αττικής </t>
+  </si>
+  <si>
+    <t>2102280343</t>
+  </si>
+  <si>
+    <t>ΑΠΟΣΤΟΛΟΠΟΥΛΟΥ ΔΑΦΝΗ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Αναπαύσεως 23, Πάτημα, 152 35 Βριλήσσια Αττικής </t>
+  </si>
+  <si>
+    <t>2106048125</t>
+  </si>
+  <si>
+    <t>6936191753</t>
+  </si>
+  <si>
+    <t>ΠΑΠΑΔΟΠΟΥΛΟΣ ΑΛΕΞΑΝΔΡΟΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Δημητρίου Λιάκου 8, 193 00 Ασπρόπυργος Αττικής </t>
+  </si>
+  <si>
+    <t>2105582465</t>
+  </si>
+  <si>
+    <t>6947695643</t>
+  </si>
+  <si>
+    <t>ΛΙΑΚΟΥΡΑΣ ΗΛΙΑΣ - L G DENTAL SMILE CARE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Παρασκευόπουλου Λεωνίδα 2, Άγιος Αντώνιος, 121 32 Περιστέρι Αττικής </t>
+  </si>
+  <si>
+    <t>2105728387</t>
+  </si>
+  <si>
+    <t>6977599709</t>
+  </si>
+  <si>
+    <t>ΠΕΤΡΟΥ ΔΗΜΗΤΡΙΟΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Αγίου Βασιλείου 12, Άγιος Βασίλειος - Ελιά, 173 43 Άγιος Δημήτριος Αττικής </t>
+  </si>
+  <si>
+    <t>2109733816</t>
+  </si>
+  <si>
+    <t>6944917002</t>
+  </si>
+  <si>
+    <t>ΒΑΒΟΥΡΑΚΗΣ ΓΕΩΡΓΙΟΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Λεωφόρος Αλεξάνδρας 91, Γκύζη, 114 74 Αθήνα Αττικής </t>
+  </si>
+  <si>
+    <t>2106437181</t>
+  </si>
+  <si>
+    <t>6972072838</t>
+  </si>
+  <si>
+    <t>ΜΕΓΑΛΟΟΙΚΟΝΟΜΟΥ ΑΝΔΡΕΑΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Λεωφόρος Βενιζέλου Ελευθέριου (τ. Λεωφόρος Θησέως) 105, Χαροκόπου, 176 72 Καλλιθέα Αττικής </t>
+  </si>
+  <si>
+    <t>2109530149</t>
+  </si>
+  <si>
+    <t>ΔΕΣΥΛΛΑΣ ΕΥΑΓΓΕΛΟΣ - STOMADENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ιφικράτους 12, Παγκράτι, 116 33 Αθήνα Αττικής </t>
+  </si>
+  <si>
+    <t>2107010839</t>
+  </si>
+  <si>
+    <t>6972184507</t>
+  </si>
+  <si>
+    <t>ΧΟΥΡΙΔΗΣ ΠΑΝΤΕΛΗΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ολύμπου 62, Φραγκοκκλησιά, 152 34 Χαλάνδρι Αττικής </t>
+  </si>
+  <si>
+    <t>2106815208</t>
+  </si>
+  <si>
+    <t>DENT-SMILE - ΜΑΡΓΕΛΛΟΥ ΠΑΡΑΣΚΕΥΗ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Γεμελιάρη Γεώργιου 6, 151 24 Μαρούσι Αττικής </t>
+  </si>
+  <si>
+    <t>2102206819</t>
+  </si>
+  <si>
+    <t>6970598860</t>
+  </si>
+  <si>
+    <t>ΠΑΝΤΑΖΙΔΗΣ ΑΡΙΣΤΟΤΕΛΗΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Βενιζέλου Ελευθερίου 16, Κέντρο, 190 09 Ραφήνα Αττικής </t>
+  </si>
+  <si>
+    <t>2294026020</t>
+  </si>
+  <si>
+    <t>6947808491</t>
+  </si>
+  <si>
+    <t>ΠΑΝΑΓΙΩΤΟΠΟΥΛΟΥ ΕΛΕΝΑ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Λεωφόρος Αυξεντίου Γρηγορίου 53, Άνω Ιλίσια, 157 71 Ζωγράφος Αττικής </t>
+  </si>
+  <si>
+    <t>2107776271</t>
+  </si>
+  <si>
+    <t>6979775452</t>
+  </si>
+  <si>
+    <t>ΛΑΒΔΑ ΜΑΡΙΤΑ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Λεωφόρος Αμαρουσίου - Χαλανδρίου 62, Παράδεισος, 151 25 Μαρούσι Αττικής </t>
+  </si>
+  <si>
+    <t>2106813823</t>
+  </si>
+  <si>
+    <t>ΜΑΣΤΟΡΑ ΑΛΕΞΑΝΔΡΑ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Λεωφόρος Κύπρου 117, Αγία Βαρβάρα, 164 51 Αργυρούπολη Αττικής </t>
+  </si>
+  <si>
+    <t>2109902263</t>
+  </si>
+  <si>
+    <t>6974615695</t>
+  </si>
+  <si>
+    <t>ENDO.CLINIC - ΠΑΠΑΔΟΥΛΗ ΚΛΑΙΡΗ DDS, MDS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Λεωφόρος Βασιλίσσης Σοφίας 105-107, 115 21 Αθήνα Αττικής </t>
+  </si>
+  <si>
+    <t>2107299909</t>
+  </si>
+  <si>
+    <t>ΑΡΓΥΡΑΚΗ ΣΤΕΦΑΝΙΑ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Τσαλδάρη Παναγή 27 &amp; Ψαθά Δημήτριου 10, Αγία Μαρίνα, 151 27 Μελίσσια Αττικής </t>
+  </si>
+  <si>
+    <t>2108105302</t>
+  </si>
+  <si>
+    <t>6945532716</t>
+  </si>
+  <si>
+    <t>ΜΑΞΟΥΤΟΓΛΟΥ ΙΟΡΔΑΝΗΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Χαροκόπου 16, 176 71 Καλλιθέα Αττικής </t>
+  </si>
+  <si>
+    <t>2109582978</t>
+  </si>
+  <si>
+    <t>6972599672</t>
+  </si>
+  <si>
+    <t>ΛΕΠΕΝΙΩΤΗ ΒΑΣΙΛΙΚΗ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Λεωφόρος Μεσογείων 392Α, Νέα Ζωή, 153 41 Αγία Παρασκευή Αττικής </t>
+  </si>
+  <si>
+    <t>2111821260</t>
+  </si>
+  <si>
+    <t>6944058631</t>
+  </si>
+  <si>
+    <t>ΔΡΟΣΟΠΟΥΛΟΣ ΗΛΙΑΣ DDS - MSc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Λεωφόρος Ηλιουπόλεως 18 &amp; Ελευθερωτών 2, 172 36 Υμηττός Αττικής </t>
+  </si>
+  <si>
+    <t>2109733900</t>
+  </si>
+  <si>
+    <t>6932655978</t>
+  </si>
+  <si>
+    <t>SMILES4KIDS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Αμαρυσίας Αρτέμιδος 15Β, Άγιος Θωμάς, 151 23 Μαρούσι Αττικής </t>
+  </si>
+  <si>
+    <t>2106107200</t>
+  </si>
+  <si>
+    <t>6937073483</t>
+  </si>
+  <si>
+    <t>ΟΙΚΟΝΟΜΟΥ ΜΙΧΑΗΛ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Τσέντνερ Φρειδερίκου 29, Ελληνορώσων, 115 25 Αθήνα Αττικής </t>
+  </si>
+  <si>
+    <t>2106753721</t>
+  </si>
+  <si>
+    <t>6971924856</t>
   </si>
 </sst>
 </file>
@@ -650,9 +1529,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="15.5703125" customWidth="1"/>
     <col min="3" max="3" width="11.5703125" customWidth="1"/>
     <col min="4" max="4" width="14.85546875" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" customWidth="1"/>
@@ -1034,6 +1914,1295 @@
         <v>86</v>
       </c>
     </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>90</v>
+      </c>
+      <c r="B25" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" t="s">
+        <v>92</v>
+      </c>
+      <c r="E25" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" t="s">
+        <v>96</v>
+      </c>
+      <c r="E26" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>103</v>
+      </c>
+      <c r="B29" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" t="s">
+        <v>105</v>
+      </c>
+      <c r="E29" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>107</v>
+      </c>
+      <c r="B30" t="s">
+        <v>108</v>
+      </c>
+      <c r="C30" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" t="s">
+        <v>109</v>
+      </c>
+      <c r="E30" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>111</v>
+      </c>
+      <c r="B31" t="s">
+        <v>112</v>
+      </c>
+      <c r="C31" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" t="s">
+        <v>113</v>
+      </c>
+      <c r="E31" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" t="s">
+        <v>116</v>
+      </c>
+      <c r="C32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>118</v>
+      </c>
+      <c r="B33" t="s">
+        <v>119</v>
+      </c>
+      <c r="C33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>121</v>
+      </c>
+      <c r="B34" t="s">
+        <v>122</v>
+      </c>
+      <c r="C34" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" t="s">
+        <v>123</v>
+      </c>
+      <c r="E34" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>125</v>
+      </c>
+      <c r="B35" t="s">
+        <v>126</v>
+      </c>
+      <c r="C35" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" t="s">
+        <v>127</v>
+      </c>
+      <c r="E35" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>129</v>
+      </c>
+      <c r="B36" t="s">
+        <v>130</v>
+      </c>
+      <c r="C36" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" t="s">
+        <v>131</v>
+      </c>
+      <c r="E36" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>133</v>
+      </c>
+      <c r="B37" t="s">
+        <v>134</v>
+      </c>
+      <c r="C37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>136</v>
+      </c>
+      <c r="B38" t="s">
+        <v>137</v>
+      </c>
+      <c r="C38" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" t="s">
+        <v>138</v>
+      </c>
+      <c r="E38" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>140</v>
+      </c>
+      <c r="B39" t="s">
+        <v>141</v>
+      </c>
+      <c r="C39" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" t="s">
+        <v>142</v>
+      </c>
+      <c r="E39" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>144</v>
+      </c>
+      <c r="B40" t="s">
+        <v>145</v>
+      </c>
+      <c r="C40" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>147</v>
+      </c>
+      <c r="B41" t="s">
+        <v>148</v>
+      </c>
+      <c r="C41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>150</v>
+      </c>
+      <c r="B42" t="s">
+        <v>151</v>
+      </c>
+      <c r="C42" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" t="s">
+        <v>152</v>
+      </c>
+      <c r="E42" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>154</v>
+      </c>
+      <c r="B43" t="s">
+        <v>155</v>
+      </c>
+      <c r="C43" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" t="s">
+        <v>156</v>
+      </c>
+      <c r="E43" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>158</v>
+      </c>
+      <c r="B44" t="s">
+        <v>159</v>
+      </c>
+      <c r="C44" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" t="s">
+        <v>160</v>
+      </c>
+      <c r="E44" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>162</v>
+      </c>
+      <c r="B45" t="s">
+        <v>163</v>
+      </c>
+      <c r="C45" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" t="s">
+        <v>164</v>
+      </c>
+      <c r="E45" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>166</v>
+      </c>
+      <c r="B46" t="s">
+        <v>167</v>
+      </c>
+      <c r="C46" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" t="s">
+        <v>168</v>
+      </c>
+      <c r="E46" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>170</v>
+      </c>
+      <c r="B47" t="s">
+        <v>171</v>
+      </c>
+      <c r="C47" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" t="s">
+        <v>172</v>
+      </c>
+      <c r="E47" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>174</v>
+      </c>
+      <c r="B48" t="s">
+        <v>175</v>
+      </c>
+      <c r="C48" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>177</v>
+      </c>
+      <c r="B49" t="s">
+        <v>178</v>
+      </c>
+      <c r="C49" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" t="s">
+        <v>179</v>
+      </c>
+      <c r="E49" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>181</v>
+      </c>
+      <c r="B50" t="s">
+        <v>182</v>
+      </c>
+      <c r="C50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" t="s">
+        <v>183</v>
+      </c>
+      <c r="E50" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>185</v>
+      </c>
+      <c r="B51" t="s">
+        <v>186</v>
+      </c>
+      <c r="C51" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" t="s">
+        <v>187</v>
+      </c>
+      <c r="E51" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>189</v>
+      </c>
+      <c r="B52" t="s">
+        <v>190</v>
+      </c>
+      <c r="C52" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" t="s">
+        <v>191</v>
+      </c>
+      <c r="E52" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>193</v>
+      </c>
+      <c r="B53" t="s">
+        <v>194</v>
+      </c>
+      <c r="C53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>196</v>
+      </c>
+      <c r="B54" t="s">
+        <v>197</v>
+      </c>
+      <c r="C54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" t="s">
+        <v>198</v>
+      </c>
+      <c r="E54" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>200</v>
+      </c>
+      <c r="B55" t="s">
+        <v>201</v>
+      </c>
+      <c r="C55" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" t="s">
+        <v>202</v>
+      </c>
+      <c r="E55" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>204</v>
+      </c>
+      <c r="B56" t="s">
+        <v>205</v>
+      </c>
+      <c r="C56" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" t="s">
+        <v>206</v>
+      </c>
+      <c r="E56" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>208</v>
+      </c>
+      <c r="B57" t="s">
+        <v>209</v>
+      </c>
+      <c r="C57" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" t="s">
+        <v>210</v>
+      </c>
+      <c r="E57" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>212</v>
+      </c>
+      <c r="B58" t="s">
+        <v>213</v>
+      </c>
+      <c r="C58" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" t="s">
+        <v>214</v>
+      </c>
+      <c r="E58" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>216</v>
+      </c>
+      <c r="B59" t="s">
+        <v>217</v>
+      </c>
+      <c r="C59" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" t="s">
+        <v>218</v>
+      </c>
+      <c r="E59" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>220</v>
+      </c>
+      <c r="B60" t="s">
+        <v>221</v>
+      </c>
+      <c r="C60" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" t="s">
+        <v>222</v>
+      </c>
+      <c r="E60" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>224</v>
+      </c>
+      <c r="B61" t="s">
+        <v>225</v>
+      </c>
+      <c r="C61" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61" t="s">
+        <v>226</v>
+      </c>
+      <c r="E61" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>228</v>
+      </c>
+      <c r="B62" t="s">
+        <v>229</v>
+      </c>
+      <c r="C62" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62" t="s">
+        <v>230</v>
+      </c>
+      <c r="E62" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>232</v>
+      </c>
+      <c r="B63" t="s">
+        <v>233</v>
+      </c>
+      <c r="C63" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" t="s">
+        <v>234</v>
+      </c>
+      <c r="E63" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>236</v>
+      </c>
+      <c r="B64" t="s">
+        <v>237</v>
+      </c>
+      <c r="C64" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" t="s">
+        <v>238</v>
+      </c>
+      <c r="E64" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>240</v>
+      </c>
+      <c r="B65" t="s">
+        <v>241</v>
+      </c>
+      <c r="C65" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65" t="s">
+        <v>242</v>
+      </c>
+      <c r="E65" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>244</v>
+      </c>
+      <c r="B66" t="s">
+        <v>245</v>
+      </c>
+      <c r="C66" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" t="s">
+        <v>246</v>
+      </c>
+      <c r="E66" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>248</v>
+      </c>
+      <c r="B67" t="s">
+        <v>249</v>
+      </c>
+      <c r="C67" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67" t="s">
+        <v>250</v>
+      </c>
+      <c r="E67" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>252</v>
+      </c>
+      <c r="B68" t="s">
+        <v>253</v>
+      </c>
+      <c r="C68" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68" t="s">
+        <v>254</v>
+      </c>
+      <c r="E68" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>256</v>
+      </c>
+      <c r="B69" t="s">
+        <v>257</v>
+      </c>
+      <c r="C69" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" t="s">
+        <v>258</v>
+      </c>
+      <c r="E69" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>260</v>
+      </c>
+      <c r="B70" t="s">
+        <v>261</v>
+      </c>
+      <c r="C70" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70" t="s">
+        <v>262</v>
+      </c>
+      <c r="E70" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>264</v>
+      </c>
+      <c r="B71" t="s">
+        <v>265</v>
+      </c>
+      <c r="C71" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>267</v>
+      </c>
+      <c r="B72" t="s">
+        <v>268</v>
+      </c>
+      <c r="C72" t="s">
+        <v>9</v>
+      </c>
+      <c r="D72" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>270</v>
+      </c>
+      <c r="B73" t="s">
+        <v>271</v>
+      </c>
+      <c r="C73" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73" t="s">
+        <v>272</v>
+      </c>
+      <c r="E73" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>274</v>
+      </c>
+      <c r="B74" t="s">
+        <v>275</v>
+      </c>
+      <c r="C74" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74" t="s">
+        <v>276</v>
+      </c>
+      <c r="E74" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>278</v>
+      </c>
+      <c r="B75" t="s">
+        <v>279</v>
+      </c>
+      <c r="C75" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75" t="s">
+        <v>280</v>
+      </c>
+      <c r="E75" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>224</v>
+      </c>
+      <c r="B76" t="s">
+        <v>282</v>
+      </c>
+      <c r="C76" t="s">
+        <v>9</v>
+      </c>
+      <c r="D76" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>224</v>
+      </c>
+      <c r="B77" t="s">
+        <v>76</v>
+      </c>
+      <c r="C77" t="s">
+        <v>9</v>
+      </c>
+      <c r="D77" t="s">
+        <v>284</v>
+      </c>
+      <c r="E77" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>286</v>
+      </c>
+      <c r="B78" t="s">
+        <v>287</v>
+      </c>
+      <c r="C78" t="s">
+        <v>9</v>
+      </c>
+      <c r="D78" t="s">
+        <v>288</v>
+      </c>
+      <c r="E78" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>290</v>
+      </c>
+      <c r="B79" t="s">
+        <v>291</v>
+      </c>
+      <c r="C79" t="s">
+        <v>9</v>
+      </c>
+      <c r="D79" t="s">
+        <v>292</v>
+      </c>
+      <c r="E79" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>294</v>
+      </c>
+      <c r="B80" t="s">
+        <v>295</v>
+      </c>
+      <c r="C80" t="s">
+        <v>9</v>
+      </c>
+      <c r="D80" t="s">
+        <v>296</v>
+      </c>
+      <c r="E80" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>298</v>
+      </c>
+      <c r="B81" t="s">
+        <v>40</v>
+      </c>
+      <c r="C81" t="s">
+        <v>9</v>
+      </c>
+      <c r="D81" t="s">
+        <v>299</v>
+      </c>
+      <c r="E81" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>301</v>
+      </c>
+      <c r="B82" t="s">
+        <v>302</v>
+      </c>
+      <c r="C82" t="s">
+        <v>9</v>
+      </c>
+      <c r="D82" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>304</v>
+      </c>
+      <c r="B83" t="s">
+        <v>305</v>
+      </c>
+      <c r="C83" t="s">
+        <v>9</v>
+      </c>
+      <c r="D83" t="s">
+        <v>306</v>
+      </c>
+      <c r="E83" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>308</v>
+      </c>
+      <c r="B84" t="s">
+        <v>309</v>
+      </c>
+      <c r="C84" t="s">
+        <v>9</v>
+      </c>
+      <c r="D84" t="s">
+        <v>310</v>
+      </c>
+      <c r="E84" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>312</v>
+      </c>
+      <c r="B85" t="s">
+        <v>313</v>
+      </c>
+      <c r="C85" t="s">
+        <v>9</v>
+      </c>
+      <c r="D85" t="s">
+        <v>314</v>
+      </c>
+      <c r="E85" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>316</v>
+      </c>
+      <c r="B86" t="s">
+        <v>317</v>
+      </c>
+      <c r="C86" t="s">
+        <v>9</v>
+      </c>
+      <c r="D86" t="s">
+        <v>318</v>
+      </c>
+      <c r="E86" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>320</v>
+      </c>
+      <c r="B87" t="s">
+        <v>321</v>
+      </c>
+      <c r="C87" t="s">
+        <v>9</v>
+      </c>
+      <c r="D87" t="s">
+        <v>322</v>
+      </c>
+      <c r="E87" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>324</v>
+      </c>
+      <c r="B88" t="s">
+        <v>325</v>
+      </c>
+      <c r="C88" t="s">
+        <v>9</v>
+      </c>
+      <c r="D88" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>327</v>
+      </c>
+      <c r="B89" t="s">
+        <v>328</v>
+      </c>
+      <c r="C89" t="s">
+        <v>9</v>
+      </c>
+      <c r="D89" t="s">
+        <v>329</v>
+      </c>
+      <c r="E89" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>331</v>
+      </c>
+      <c r="B90" t="s">
+        <v>332</v>
+      </c>
+      <c r="C90" t="s">
+        <v>9</v>
+      </c>
+      <c r="D90" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>334</v>
+      </c>
+      <c r="B91" t="s">
+        <v>335</v>
+      </c>
+      <c r="C91" t="s">
+        <v>9</v>
+      </c>
+      <c r="D91" t="s">
+        <v>336</v>
+      </c>
+      <c r="E91" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>338</v>
+      </c>
+      <c r="B92" t="s">
+        <v>339</v>
+      </c>
+      <c r="C92" t="s">
+        <v>9</v>
+      </c>
+      <c r="D92" t="s">
+        <v>340</v>
+      </c>
+      <c r="E92" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>342</v>
+      </c>
+      <c r="B93" t="s">
+        <v>343</v>
+      </c>
+      <c r="C93" t="s">
+        <v>9</v>
+      </c>
+      <c r="D93" t="s">
+        <v>344</v>
+      </c>
+      <c r="E93" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>346</v>
+      </c>
+      <c r="B94" t="s">
+        <v>347</v>
+      </c>
+      <c r="C94" t="s">
+        <v>9</v>
+      </c>
+      <c r="D94" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>349</v>
+      </c>
+      <c r="B95" t="s">
+        <v>350</v>
+      </c>
+      <c r="C95" t="s">
+        <v>9</v>
+      </c>
+      <c r="D95" t="s">
+        <v>351</v>
+      </c>
+      <c r="E95" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>353</v>
+      </c>
+      <c r="B96" t="s">
+        <v>354</v>
+      </c>
+      <c r="C96" t="s">
+        <v>9</v>
+      </c>
+      <c r="D96" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>356</v>
+      </c>
+      <c r="B97" t="s">
+        <v>357</v>
+      </c>
+      <c r="C97" t="s">
+        <v>9</v>
+      </c>
+      <c r="D97" t="s">
+        <v>358</v>
+      </c>
+      <c r="E97" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>360</v>
+      </c>
+      <c r="B98" t="s">
+        <v>361</v>
+      </c>
+      <c r="C98" t="s">
+        <v>9</v>
+      </c>
+      <c r="D98" t="s">
+        <v>362</v>
+      </c>
+      <c r="E98" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>364</v>
+      </c>
+      <c r="B99" t="s">
+        <v>365</v>
+      </c>
+      <c r="C99" t="s">
+        <v>9</v>
+      </c>
+      <c r="D99" t="s">
+        <v>366</v>
+      </c>
+      <c r="E99" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>368</v>
+      </c>
+      <c r="B100" t="s">
+        <v>369</v>
+      </c>
+      <c r="C100" t="s">
+        <v>9</v>
+      </c>
+      <c r="D100" t="s">
+        <v>370</v>
+      </c>
+      <c r="E100" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>372</v>
+      </c>
+      <c r="B101" t="s">
+        <v>373</v>
+      </c>
+      <c r="C101" t="s">
+        <v>9</v>
+      </c>
+      <c r="D101" t="s">
+        <v>374</v>
+      </c>
+      <c r="E101" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>376</v>
+      </c>
+      <c r="B102" t="s">
+        <v>377</v>
+      </c>
+      <c r="C102" t="s">
+        <v>9</v>
+      </c>
+      <c r="D102" t="s">
+        <v>378</v>
+      </c>
+      <c r="E102" t="s">
+        <v>379</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
